--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-messageHeader.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-messageHeader.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.1</t>
+    <t>5.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T10:10:10+00:00</t>
+    <t>2026-02-13T11:55:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2002,7 +2002,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>168</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>180</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>196</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>264</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>270</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>287</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>296</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>301</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>310</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>311</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>314</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>318</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>322</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>325</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>327</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>333</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>334</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>336</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>354</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>386</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>440</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>447</v>
       </c>
@@ -12115,12 +12115,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM93">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-messageHeader.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-messageHeader.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.2</t>
+    <t>5.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T11:55:29+00:00</t>
+    <t>2026-06-03T09:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1413,7 +1413,7 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 medcom-carecommunication-definition-url:SHALL reference a MedCom CareCommunication MessageDefinition whose canonical URL starts with
-http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition|5. — that is, any version 5.x of the message definition. The current minor version the sender uses must be added in the end of the definition. {matches('^http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition|5[.][0-9]{1,2}$')}</t>
+http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition|5. — that is, any version 5.x of the message definition. The current minor version the sender uses must be added in the end of the definition. {matches('^http://medcomfhir.dk/ig/messagedefinitions/MessageDefinition/MedComCareCommunicationMessageDefinition[|]5[.][0-9]{1,2}$')}</t>
   </si>
   <si>
     <t>Not directly supported.</t>

--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-messageHeader.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-messageHeader.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.3</t>
+    <t>5.0.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:32:39+00:00</t>
+    <t>2026-06-05T08:11:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
